--- a/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_95.xlsx
+++ b/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_95.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\LApredict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6399419F-470C-4D2B-B0B3-8EAF4B7F3577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042A6877-E45D-4EBB-9E55-4DE18BF92788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31960" yWindow="8600" windowWidth="23660" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="valid" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">valid!$A$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>Total Rows</t>
   </si>
@@ -84,9 +85,6 @@
   </si>
   <si>
     <t>recall fault-prone</t>
-  </si>
-  <si>
-    <t>Test avg</t>
   </si>
   <si>
     <t>Valid avg</t>
@@ -146,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -154,6 +152,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -565,15 +564,15 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N34" si="0">H3/B3</f>
+        <f>H3/B3</f>
         <v>2.0345252774352653E-2</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O34" si="1">I3/C3</f>
+        <f>I3/C3</f>
         <v>2.0754716981132074E-2</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P34" si="2">J3/D3</f>
+        <f>J3/D3</f>
         <v>0</v>
       </c>
     </row>
@@ -618,15 +617,15 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f t="shared" si="0"/>
+        <f>H4/B4</f>
         <v>2.3809523809523808E-2</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
+        <f>I4/C4</f>
         <v>2.4343369634849454E-2</v>
       </c>
       <c r="P4">
-        <f t="shared" si="2"/>
+        <f>J4/D4</f>
         <v>0</v>
       </c>
     </row>
@@ -671,15 +670,15 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f t="shared" si="0"/>
+        <f>H5/B5</f>
         <v>1.4084507042253521E-2</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
+        <f>I5/C5</f>
         <v>1.4330218068535825E-2</v>
       </c>
       <c r="P5">
-        <f t="shared" si="2"/>
+        <f>J5/D5</f>
         <v>0</v>
       </c>
     </row>
@@ -724,15 +723,15 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <f t="shared" si="0"/>
+        <f>H6/B6</f>
         <v>1.5950920245398775E-2</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f>I6/C6</f>
         <v>1.5703517587939697E-2</v>
       </c>
       <c r="P6">
-        <f t="shared" si="2"/>
+        <f>J6/D6</f>
         <v>2.6315789473684209E-2</v>
       </c>
     </row>
@@ -777,15 +776,15 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="0"/>
+        <f>H7/B7</f>
         <v>1.3647642679900745E-2</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f>I7/C7</f>
         <v>1.3950538998097653E-2</v>
       </c>
       <c r="P7">
-        <f t="shared" si="2"/>
+        <f>J7/D7</f>
         <v>0</v>
       </c>
     </row>
@@ -830,15 +829,15 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="0"/>
+        <f>H8/B8</f>
         <v>2.1844660194174758E-2</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
+        <f>I8/C8</f>
         <v>2.2167487684729065E-2</v>
       </c>
       <c r="P8">
-        <f t="shared" si="2"/>
+        <f>J8/D8</f>
         <v>0</v>
       </c>
     </row>
@@ -883,15 +882,15 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="0"/>
+        <f>H9/B9</f>
         <v>1.6E-2</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f>I9/C9</f>
         <v>1.6219588271990017E-2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="2"/>
+        <f>J9/D9</f>
         <v>0</v>
       </c>
     </row>
@@ -936,15 +935,15 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="0"/>
+        <f>H10/B10</f>
         <v>2.2713321055862493E-2</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f>I10/C10</f>
         <v>2.282541640962369E-2</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f>J10/D10</f>
         <v>0</v>
       </c>
     </row>
@@ -989,15 +988,15 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="0"/>
+        <f>H11/B11</f>
         <v>1.653398652786283E-2</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f>I11/C11</f>
         <v>1.6843418590143482E-2</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f>J11/D11</f>
         <v>0</v>
       </c>
     </row>
@@ -1042,15 +1041,15 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="0"/>
+        <f>H12/B12</f>
         <v>1.508485229415462E-2</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f>I12/C12</f>
         <v>1.5345268542199489E-2</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f>J12/D12</f>
         <v>0</v>
       </c>
     </row>
@@ -1095,15 +1094,15 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="0"/>
+        <f>H13/B13</f>
         <v>1.5290519877675841E-2</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f>I13/C13</f>
         <v>1.554726368159204E-2</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
+        <f>J13/D13</f>
         <v>0</v>
       </c>
     </row>
@@ -1148,15 +1147,15 @@
         <v>1</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
+        <f>H14/B14</f>
         <v>1.547029702970297E-2</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
+        <f>I14/C14</f>
         <v>1.5037593984962405E-2</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
+        <f>J14/D14</f>
         <v>0.05</v>
       </c>
     </row>
@@ -1201,15 +1200,15 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="0"/>
+        <f>H15/B15</f>
         <v>1.431238332296204E-2</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f>I15/C15</f>
         <v>1.44745122718691E-2</v>
       </c>
       <c r="P15">
-        <f t="shared" si="2"/>
+        <f>J15/D15</f>
         <v>0</v>
       </c>
     </row>
@@ -1254,15 +1253,15 @@
         <v>1</v>
       </c>
       <c r="N16">
-        <f t="shared" si="0"/>
+        <f>H16/B16</f>
         <v>1.8879798615481436E-2</v>
       </c>
       <c r="O16">
-        <f t="shared" si="1"/>
+        <f>I16/C16</f>
         <v>1.8554062699936022E-2</v>
       </c>
       <c r="P16">
-        <f t="shared" si="2"/>
+        <f>J16/D16</f>
         <v>3.8461538461538464E-2</v>
       </c>
     </row>
@@ -1307,15 +1306,15 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="0"/>
+        <f>H17/B17</f>
         <v>2.2655758338577723E-2</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
+        <f>I17/C17</f>
         <v>2.3091725465041693E-2</v>
       </c>
       <c r="P17">
-        <f t="shared" si="2"/>
+        <f>J17/D17</f>
         <v>0</v>
       </c>
     </row>
@@ -1360,15 +1359,15 @@
         <v>1</v>
       </c>
       <c r="N18">
-        <f t="shared" si="0"/>
+        <f>H18/B18</f>
         <v>2.0291693088142042E-2</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
+        <f>I18/C18</f>
         <v>1.9442644199611146E-2</v>
       </c>
       <c r="P18">
-        <f t="shared" si="2"/>
+        <f>J18/D18</f>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
@@ -1413,15 +1412,15 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <f t="shared" si="0"/>
+        <f>H19/B19</f>
         <v>1.6109045848822799E-2</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
+        <f>I19/C19</f>
         <v>1.6372795969773299E-2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="2"/>
+        <f>J19/D19</f>
         <v>0</v>
       </c>
     </row>
@@ -1466,15 +1465,15 @@
         <v>1</v>
       </c>
       <c r="N20">
-        <f t="shared" si="0"/>
+        <f>H20/B20</f>
         <v>1.8270401948842874E-2</v>
       </c>
       <c r="O20">
-        <f t="shared" si="1"/>
+        <f>I20/C20</f>
         <v>1.7802332719459791E-2</v>
       </c>
       <c r="P20">
-        <f t="shared" si="2"/>
+        <f>J20/D20</f>
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
@@ -1519,15 +1518,15 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="0"/>
+        <f>H21/B21</f>
         <v>1.7262638717632551E-2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
+        <f>I21/C21</f>
         <v>1.7632241813602016E-2</v>
       </c>
       <c r="P21">
-        <f t="shared" si="2"/>
+        <f>J21/D21</f>
         <v>0</v>
       </c>
     </row>
@@ -1572,15 +1571,15 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <f t="shared" si="0"/>
+        <f>H22/B22</f>
         <v>1.678060907395898E-2</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
+        <f>I22/C22</f>
         <v>1.6938519447929738E-2</v>
       </c>
       <c r="P22">
-        <f t="shared" si="2"/>
+        <f>J22/D22</f>
         <v>0</v>
       </c>
     </row>
@@ -1625,15 +1624,15 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <f t="shared" si="0"/>
+        <f>H23/B23</f>
         <v>1.6229712858926344E-2</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
+        <f>I23/C23</f>
         <v>1.6549968173138127E-2</v>
       </c>
       <c r="P23">
-        <f t="shared" si="2"/>
+        <f>J23/D23</f>
         <v>0</v>
       </c>
     </row>
@@ -1678,15 +1677,15 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <f t="shared" si="0"/>
+        <f>H24/B24</f>
         <v>2.1604938271604937E-2</v>
       </c>
       <c r="O24">
-        <f t="shared" si="1"/>
+        <f>I24/C24</f>
         <v>2.20125786163522E-2</v>
       </c>
       <c r="P24">
-        <f t="shared" si="2"/>
+        <f>J24/D24</f>
         <v>0</v>
       </c>
     </row>
@@ -1731,15 +1730,15 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <f t="shared" si="0"/>
+        <f>H25/B25</f>
         <v>1.9619865113427344E-2</v>
       </c>
       <c r="O25">
-        <f t="shared" si="1"/>
+        <f>I25/C25</f>
         <v>1.9112207151664611E-2</v>
       </c>
       <c r="P25">
-        <f t="shared" si="2"/>
+        <f>J25/D25</f>
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -1784,15 +1783,15 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <f t="shared" si="0"/>
+        <f>H26/B26</f>
         <v>1.5970515970515971E-2</v>
       </c>
       <c r="O26">
-        <f t="shared" si="1"/>
+        <f>I26/C26</f>
         <v>1.6239850093691444E-2</v>
       </c>
       <c r="P26">
-        <f t="shared" si="2"/>
+        <f>J26/D26</f>
         <v>0</v>
       </c>
     </row>
@@ -1837,15 +1836,15 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <f t="shared" si="0"/>
+        <f>H27/B27</f>
         <v>1.9962570180910792E-2</v>
       </c>
       <c r="O27">
-        <f t="shared" si="1"/>
+        <f>I27/C27</f>
         <v>1.9632678910702975E-2</v>
       </c>
       <c r="P27">
-        <f t="shared" si="2"/>
+        <f>J27/D27</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -1890,15 +1889,15 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <f t="shared" si="0"/>
+        <f>H28/B28</f>
         <v>1.8552875695732839E-2</v>
       </c>
       <c r="O28">
-        <f t="shared" si="1"/>
+        <f>I28/C28</f>
         <v>1.8238993710691823E-2</v>
       </c>
       <c r="P28">
-        <f t="shared" si="2"/>
+        <f>J28/D28</f>
         <v>3.7037037037037035E-2</v>
       </c>
     </row>
@@ -1943,15 +1942,15 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <f t="shared" si="0"/>
+        <f>H29/B29</f>
         <v>1.4501891551071878E-2</v>
       </c>
       <c r="O29">
-        <f t="shared" si="1"/>
+        <f>I29/C29</f>
         <v>1.4819587628865979E-2</v>
       </c>
       <c r="P29">
-        <f t="shared" si="2"/>
+        <f>J29/D29</f>
         <v>0</v>
       </c>
     </row>
@@ -1996,15 +1995,15 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <f t="shared" si="0"/>
+        <f>H30/B30</f>
         <v>1.9801980198019802E-2</v>
       </c>
       <c r="O30">
-        <f t="shared" si="1"/>
+        <f>I30/C30</f>
         <v>2.0227560050568902E-2</v>
       </c>
       <c r="P30">
-        <f t="shared" si="2"/>
+        <f>J30/D30</f>
         <v>0</v>
       </c>
     </row>
@@ -2049,15 +2048,15 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <f t="shared" si="0"/>
+        <f>H31/B31</f>
         <v>1.858736059479554E-2</v>
       </c>
       <c r="O31">
-        <f t="shared" si="1"/>
+        <f>I31/C31</f>
         <v>1.8879798615481436E-2</v>
       </c>
       <c r="P31">
-        <f t="shared" si="2"/>
+        <f>J31/D31</f>
         <v>0</v>
       </c>
     </row>
@@ -2102,15 +2101,15 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <f t="shared" si="0"/>
+        <f>H32/B32</f>
         <v>1.2962962962962963E-2</v>
       </c>
       <c r="O32">
-        <f t="shared" si="1"/>
+        <f>I32/C32</f>
         <v>1.3190954773869347E-2</v>
       </c>
       <c r="P32">
-        <f t="shared" si="2"/>
+        <f>J32/D32</f>
         <v>0</v>
       </c>
     </row>
@@ -2155,15 +2154,15 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <f t="shared" si="0"/>
+        <f>H33/B33</f>
         <v>1.8738288569643973E-2</v>
       </c>
       <c r="O33">
-        <f t="shared" si="1"/>
+        <f>I33/C33</f>
         <v>1.9096117122851686E-2</v>
       </c>
       <c r="P33">
-        <f t="shared" si="2"/>
+        <f>J33/D33</f>
         <v>0</v>
       </c>
     </row>
@@ -2208,15 +2207,15 @@
         <v>1</v>
       </c>
       <c r="N34">
-        <f t="shared" si="0"/>
+        <f>H34/B34</f>
         <v>1.4171287738755391E-2</v>
       </c>
       <c r="O34">
-        <f t="shared" si="1"/>
+        <f>I34/C34</f>
         <v>1.3862633900441084E-2</v>
       </c>
       <c r="P34">
-        <f t="shared" si="2"/>
+        <f>J34/D34</f>
         <v>2.7777777777777776E-2</v>
       </c>
     </row>
@@ -2261,15 +2260,15 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <f t="shared" ref="N35:N66" si="3">H35/B35</f>
+        <f>H35/B35</f>
         <v>1.8023617153511497E-2</v>
       </c>
       <c r="O35">
-        <f t="shared" ref="O35:O66" si="4">I35/C35</f>
+        <f>I35/C35</f>
         <v>1.8389346861128725E-2</v>
       </c>
       <c r="P35">
-        <f t="shared" ref="P35:P66" si="5">J35/D35</f>
+        <f>J35/D35</f>
         <v>0</v>
       </c>
     </row>
@@ -2314,15 +2313,15 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <f t="shared" si="3"/>
+        <f>H36/B36</f>
         <v>1.7316017316017316E-2</v>
       </c>
       <c r="O36">
-        <f t="shared" si="4"/>
+        <f>I36/C36</f>
         <v>1.7576898932831136E-2</v>
       </c>
       <c r="P36">
-        <f t="shared" si="5"/>
+        <f>J36/D36</f>
         <v>0</v>
       </c>
     </row>
@@ -2367,15 +2366,15 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <f t="shared" si="3"/>
+        <f>H37/B37</f>
         <v>1.5834348355663823E-2</v>
       </c>
       <c r="O37">
-        <f t="shared" si="4"/>
+        <f>I37/C37</f>
         <v>1.6109045848822799E-2</v>
       </c>
       <c r="P37">
-        <f t="shared" si="5"/>
+        <f>J37/D37</f>
         <v>0</v>
       </c>
     </row>
@@ -2420,15 +2419,15 @@
         <v>1</v>
       </c>
       <c r="N38">
-        <f t="shared" si="3"/>
+        <f>H38/B38</f>
         <v>1.6280525986224169E-2</v>
       </c>
       <c r="O38">
-        <f t="shared" si="4"/>
+        <f>I38/C38</f>
         <v>1.5964240102171137E-2</v>
       </c>
       <c r="P38">
-        <f t="shared" si="5"/>
+        <f>J38/D38</f>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
@@ -2473,15 +2472,15 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <f t="shared" si="3"/>
+        <f>H39/B39</f>
         <v>1.9183168316831683E-2</v>
       </c>
       <c r="O39">
-        <f t="shared" si="4"/>
+        <f>I39/C39</f>
         <v>1.9254658385093167E-2</v>
       </c>
       <c r="P39">
-        <f t="shared" si="5"/>
+        <f>J39/D39</f>
         <v>0</v>
       </c>
     </row>
@@ -2526,15 +2525,15 @@
         <v>1</v>
       </c>
       <c r="N40">
-        <f t="shared" si="3"/>
+        <f>H40/B40</f>
         <v>1.4760147601476014E-2</v>
       </c>
       <c r="O40">
-        <f t="shared" si="4"/>
+        <f>I40/C40</f>
         <v>1.4429109159347553E-2</v>
       </c>
       <c r="P40">
-        <f t="shared" si="5"/>
+        <f>J40/D40</f>
         <v>3.125E-2</v>
       </c>
     </row>
@@ -2579,15 +2578,15 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <f t="shared" si="3"/>
+        <f>H41/B41</f>
         <v>1.7125382262996942E-2</v>
       </c>
       <c r="O41">
-        <f t="shared" si="4"/>
+        <f>I41/C41</f>
         <v>1.7478152309612985E-2</v>
       </c>
       <c r="P41">
-        <f t="shared" si="5"/>
+        <f>J41/D41</f>
         <v>0</v>
       </c>
     </row>
@@ -2632,15 +2631,15 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <f t="shared" si="3"/>
+        <f>H42/B42</f>
         <v>1.6676961087090797E-2</v>
       </c>
       <c r="O42">
-        <f t="shared" si="4"/>
+        <f>I42/C42</f>
         <v>1.7023959646910468E-2</v>
       </c>
       <c r="P42">
-        <f t="shared" si="5"/>
+        <f>J42/D42</f>
         <v>0</v>
       </c>
     </row>
@@ -2685,15 +2684,15 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <f t="shared" si="3"/>
+        <f>H43/B43</f>
         <v>1.1117974058060531E-2</v>
       </c>
       <c r="O43">
-        <f t="shared" si="4"/>
+        <f>I43/C43</f>
         <v>1.1327879169288861E-2</v>
       </c>
       <c r="P43">
-        <f t="shared" si="5"/>
+        <f>J43/D43</f>
         <v>0</v>
       </c>
     </row>
@@ -2738,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="N44">
-        <f t="shared" si="3"/>
+        <f>H44/B44</f>
         <v>1.6615384615384615E-2</v>
       </c>
       <c r="O44">
-        <f t="shared" si="4"/>
+        <f>I44/C44</f>
         <v>1.6864459712679577E-2</v>
       </c>
       <c r="P44">
-        <f t="shared" si="5"/>
+        <f>J44/D44</f>
         <v>0</v>
       </c>
     </row>
@@ -2791,15 +2790,15 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <f t="shared" si="3"/>
+        <f>H45/B45</f>
         <v>1.4906832298136646E-2</v>
       </c>
       <c r="O45">
-        <f t="shared" si="4"/>
+        <f>I45/C45</f>
         <v>1.5122873345935728E-2</v>
       </c>
       <c r="P45">
-        <f t="shared" si="5"/>
+        <f>J45/D45</f>
         <v>0</v>
       </c>
     </row>
@@ -2844,15 +2843,15 @@
         <v>0</v>
       </c>
       <c r="N46">
-        <f t="shared" si="3"/>
+        <f>H46/B46</f>
         <v>1.6959798994974875E-2</v>
       </c>
       <c r="O46">
-        <f t="shared" si="4"/>
+        <f>I46/C46</f>
         <v>1.7197452229299363E-2</v>
       </c>
       <c r="P46">
-        <f t="shared" si="5"/>
+        <f>J46/D46</f>
         <v>0</v>
       </c>
     </row>
@@ -2897,15 +2896,15 @@
         <v>0.5</v>
       </c>
       <c r="N47">
-        <f t="shared" si="3"/>
+        <f>H47/B47</f>
         <v>1.8937080024434942E-2</v>
       </c>
       <c r="O47">
-        <f t="shared" si="4"/>
+        <f>I47/C47</f>
         <v>1.86799501867995E-2</v>
       </c>
       <c r="P47">
-        <f t="shared" si="5"/>
+        <f>J47/D47</f>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
@@ -2950,15 +2949,15 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <f t="shared" si="3"/>
+        <f>H48/B48</f>
         <v>2.0974706971005553E-2</v>
       </c>
       <c r="O48">
-        <f t="shared" si="4"/>
+        <f>I48/C48</f>
         <v>2.1263289555972485E-2</v>
       </c>
       <c r="P48">
-        <f t="shared" si="5"/>
+        <f>J48/D48</f>
         <v>0</v>
       </c>
     </row>
@@ -3003,15 +3002,15 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <f t="shared" si="3"/>
+        <f>H49/B49</f>
         <v>1.7879161528976572E-2</v>
       </c>
       <c r="O49">
-        <f t="shared" si="4"/>
+        <f>I49/C49</f>
         <v>1.8216080402010049E-2</v>
       </c>
       <c r="P49">
-        <f t="shared" si="5"/>
+        <f>J49/D49</f>
         <v>0</v>
       </c>
     </row>
@@ -3056,15 +3055,15 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <f t="shared" si="3"/>
+        <f>H50/B50</f>
         <v>1.5489467162329617E-2</v>
       </c>
       <c r="O50">
-        <f t="shared" si="4"/>
+        <f>I50/C50</f>
         <v>1.452020202020202E-2</v>
       </c>
       <c r="P50">
-        <f t="shared" si="5"/>
+        <f>J50/D50</f>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
@@ -3109,15 +3108,15 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <f t="shared" si="3"/>
+        <f>H51/B51</f>
         <v>1.86219739292365E-2</v>
       </c>
       <c r="O51">
-        <f t="shared" si="4"/>
+        <f>I51/C51</f>
         <v>1.831964624131396E-2</v>
       </c>
       <c r="P51">
-        <f t="shared" si="5"/>
+        <f>J51/D51</f>
         <v>3.5714285714285712E-2</v>
       </c>
     </row>
@@ -3162,15 +3161,15 @@
         <v>0</v>
       </c>
       <c r="N52">
-        <f t="shared" si="3"/>
+        <f>H52/B52</f>
         <v>1.7813267813267815E-2</v>
       </c>
       <c r="O52">
-        <f t="shared" si="4"/>
+        <f>I52/C52</f>
         <v>1.8170426065162906E-2</v>
       </c>
       <c r="P52">
-        <f t="shared" si="5"/>
+        <f>J52/D52</f>
         <v>0</v>
       </c>
     </row>
@@ -3215,15 +3214,15 @@
         <v>1</v>
       </c>
       <c r="N53">
-        <f t="shared" si="3"/>
+        <f>H53/B53</f>
         <v>1.7901234567901235E-2</v>
       </c>
       <c r="O53">
-        <f t="shared" si="4"/>
+        <f>I53/C53</f>
         <v>1.7654476670870115E-2</v>
       </c>
       <c r="P53">
-        <f t="shared" si="5"/>
+        <f>J53/D53</f>
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
@@ -3268,15 +3267,15 @@
         <v>0</v>
       </c>
       <c r="N54">
-        <f t="shared" si="3"/>
+        <f>H54/B54</f>
         <v>1.5499070055796652E-2</v>
       </c>
       <c r="O54">
-        <f t="shared" si="4"/>
+        <f>I54/C54</f>
         <v>1.5733165512901194E-2</v>
       </c>
       <c r="P54">
-        <f t="shared" si="5"/>
+        <f>J54/D54</f>
         <v>0</v>
       </c>
     </row>
@@ -3321,15 +3320,15 @@
         <v>0</v>
       </c>
       <c r="N55">
-        <f t="shared" si="3"/>
+        <f>H55/B55</f>
         <v>1.7489069331667707E-2</v>
       </c>
       <c r="O55">
-        <f t="shared" si="4"/>
+        <f>I55/C55</f>
         <v>1.7755231452124286E-2</v>
       </c>
       <c r="P55">
-        <f t="shared" si="5"/>
+        <f>J55/D55</f>
         <v>0</v>
       </c>
     </row>
@@ -3374,15 +3373,15 @@
         <v>0</v>
       </c>
       <c r="N56">
-        <f t="shared" si="3"/>
+        <f>H56/B56</f>
         <v>1.3521819299323909E-2</v>
       </c>
       <c r="O56">
-        <f t="shared" si="4"/>
+        <f>I56/C56</f>
         <v>1.3732833957553059E-2</v>
       </c>
       <c r="P56">
-        <f t="shared" si="5"/>
+        <f>J56/D56</f>
         <v>0</v>
       </c>
     </row>
@@ -3427,15 +3426,15 @@
         <v>0</v>
       </c>
       <c r="N57">
-        <f t="shared" si="3"/>
+        <f>H57/B57</f>
         <v>2.002503128911139E-2</v>
       </c>
       <c r="O57">
-        <f t="shared" si="4"/>
+        <f>I57/C57</f>
         <v>2.0395156150414276E-2</v>
       </c>
       <c r="P57">
-        <f t="shared" si="5"/>
+        <f>J57/D57</f>
         <v>0</v>
       </c>
     </row>
@@ -3480,15 +3479,15 @@
         <v>0</v>
       </c>
       <c r="N58">
-        <f t="shared" si="3"/>
+        <f>H58/B58</f>
         <v>2.4691358024691357E-2</v>
       </c>
       <c r="O58">
-        <f t="shared" si="4"/>
+        <f>I58/C58</f>
         <v>2.5173064820641914E-2</v>
       </c>
       <c r="P58">
-        <f t="shared" si="5"/>
+        <f>J58/D58</f>
         <v>0</v>
       </c>
     </row>
@@ -3533,15 +3532,15 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <f t="shared" si="3"/>
+        <f>H59/B59</f>
         <v>2.4875621890547265E-2</v>
       </c>
       <c r="O59">
-        <f t="shared" si="4"/>
+        <f>I59/C59</f>
         <v>2.5364616360177554E-2</v>
       </c>
       <c r="P59">
-        <f t="shared" si="5"/>
+        <f>J59/D59</f>
         <v>0</v>
       </c>
     </row>
@@ -3586,15 +3585,15 @@
         <v>1</v>
       </c>
       <c r="N60">
-        <f t="shared" si="3"/>
+        <f>H60/B60</f>
         <v>1.8102372034956304E-2</v>
       </c>
       <c r="O60">
-        <f t="shared" si="4"/>
+        <f>I60/C60</f>
         <v>1.7891373801916934E-2</v>
       </c>
       <c r="P60">
-        <f t="shared" si="5"/>
+        <f>J60/D60</f>
         <v>2.7027027027027029E-2</v>
       </c>
     </row>
@@ -3639,15 +3638,15 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <f t="shared" si="3"/>
+        <f>H61/B61</f>
         <v>1.0442260442260442E-2</v>
       </c>
       <c r="O61">
-        <f t="shared" si="4"/>
+        <f>I61/C61</f>
         <v>1.0480887792848335E-2</v>
       </c>
       <c r="P61">
-        <f t="shared" si="5"/>
+        <f>J61/D61</f>
         <v>0</v>
       </c>
     </row>
@@ -3692,15 +3691,15 @@
         <v>1</v>
       </c>
       <c r="N62">
-        <f t="shared" si="3"/>
+        <f>H62/B62</f>
         <v>2.1000617665225447E-2</v>
       </c>
       <c r="O62">
-        <f t="shared" si="4"/>
+        <f>I62/C62</f>
         <v>2.0663744520976832E-2</v>
       </c>
       <c r="P62">
-        <f t="shared" si="5"/>
+        <f>J62/D62</f>
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
@@ -3745,15 +3744,15 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <f t="shared" si="3"/>
+        <f>H63/B63</f>
         <v>1.3571869216533004E-2</v>
       </c>
       <c r="O63">
-        <f t="shared" si="4"/>
+        <f>I63/C63</f>
         <v>1.3810420590081607E-2</v>
       </c>
       <c r="P63">
-        <f t="shared" si="5"/>
+        <f>J63/D63</f>
         <v>0</v>
       </c>
     </row>
@@ -3798,15 +3797,15 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <f t="shared" si="3"/>
+        <f>H64/B64</f>
         <v>1.9218846869187848E-2</v>
       </c>
       <c r="O64">
-        <f t="shared" si="4"/>
+        <f>I64/C64</f>
         <v>1.9375E-2</v>
       </c>
       <c r="P64">
-        <f t="shared" si="5"/>
+        <f>J64/D64</f>
         <v>0</v>
       </c>
     </row>
@@ -3851,15 +3850,15 @@
         <v>0</v>
       </c>
       <c r="N65">
-        <f t="shared" si="3"/>
+        <f>H65/B65</f>
         <v>1.7348203221809171E-2</v>
       </c>
       <c r="O65">
-        <f t="shared" si="4"/>
+        <f>I65/C65</f>
         <v>1.7489069331667707E-2</v>
       </c>
       <c r="P65">
-        <f t="shared" si="5"/>
+        <f>J65/D65</f>
         <v>0</v>
       </c>
     </row>
@@ -3904,15 +3903,15 @@
         <v>0</v>
       </c>
       <c r="N66">
-        <f t="shared" si="3"/>
+        <f>H66/B66</f>
         <v>1.5337423312883436E-2</v>
       </c>
       <c r="O66">
-        <f t="shared" si="4"/>
+        <f>I66/C66</f>
         <v>1.5576323987538941E-2</v>
       </c>
       <c r="P66">
-        <f t="shared" si="5"/>
+        <f>J66/D66</f>
         <v>0</v>
       </c>
     </row>
@@ -3957,15 +3956,15 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <f t="shared" ref="N67:N98" si="6">H67/B67</f>
+        <f>H67/B67</f>
         <v>1.723076923076923E-2</v>
       </c>
       <c r="O67">
-        <f t="shared" ref="O67:O98" si="7">I67/C67</f>
+        <f>I67/C67</f>
         <v>1.759899434318039E-2</v>
       </c>
       <c r="P67">
-        <f t="shared" ref="P67:P98" si="8">J67/D67</f>
+        <f>J67/D67</f>
         <v>0</v>
       </c>
     </row>
@@ -4010,15 +4009,15 @@
         <v>1</v>
       </c>
       <c r="N68">
-        <f t="shared" si="6"/>
+        <f>H68/B68</f>
         <v>2.1551724137931036E-2</v>
       </c>
       <c r="O68">
-        <f t="shared" si="7"/>
+        <f>I68/C68</f>
         <v>2.1250000000000002E-2</v>
       </c>
       <c r="P68">
-        <f t="shared" si="8"/>
+        <f>J68/D68</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -4063,15 +4062,15 @@
         <v>1</v>
       </c>
       <c r="N69">
-        <f t="shared" si="6"/>
+        <f>H69/B69</f>
         <v>1.5733165512901194E-2</v>
       </c>
       <c r="O69">
-        <f t="shared" si="7"/>
+        <f>I69/C69</f>
         <v>1.5384615384615385E-2</v>
       </c>
       <c r="P69">
-        <f t="shared" si="8"/>
+        <f>J69/D69</f>
         <v>3.4482758620689655E-2</v>
       </c>
     </row>
@@ -4116,15 +4115,15 @@
         <v>0</v>
       </c>
       <c r="N70">
-        <f t="shared" si="6"/>
+        <f>H70/B70</f>
         <v>1.9218846869187848E-2</v>
       </c>
       <c r="O70">
-        <f t="shared" si="7"/>
+        <f>I70/C70</f>
         <v>1.9583070120025269E-2</v>
       </c>
       <c r="P70">
-        <f t="shared" si="8"/>
+        <f>J70/D70</f>
         <v>0</v>
       </c>
     </row>
@@ -4169,15 +4168,15 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <f t="shared" si="6"/>
+        <f>H71/B71</f>
         <v>1.7879161528976572E-2</v>
       </c>
       <c r="O71">
-        <f t="shared" si="7"/>
+        <f>I71/C71</f>
         <v>1.7412935323383085E-2</v>
       </c>
       <c r="P71">
-        <f t="shared" si="8"/>
+        <f>J71/D71</f>
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
@@ -4222,15 +4221,15 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <f t="shared" si="6"/>
+        <f>H72/B72</f>
         <v>2.2374145431945307E-2</v>
       </c>
       <c r="O72">
-        <f t="shared" si="7"/>
+        <f>I72/C72</f>
         <v>2.2741629816803537E-2</v>
       </c>
       <c r="P72">
-        <f t="shared" si="8"/>
+        <f>J72/D72</f>
         <v>0</v>
       </c>
     </row>
@@ -4275,15 +4274,15 @@
         <v>0</v>
       </c>
       <c r="N73">
-        <f t="shared" si="6"/>
+        <f>H73/B73</f>
         <v>1.8427518427518427E-2</v>
       </c>
       <c r="O73">
-        <f t="shared" si="7"/>
+        <f>I73/C73</f>
         <v>1.8738288569643973E-2</v>
       </c>
       <c r="P73">
-        <f t="shared" si="8"/>
+        <f>J73/D73</f>
         <v>0</v>
       </c>
     </row>
@@ -4328,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="N74">
-        <f t="shared" si="6"/>
+        <f>H74/B74</f>
         <v>1.9053472649047325E-2</v>
       </c>
       <c r="O74">
-        <f t="shared" si="7"/>
+        <f>I74/C74</f>
         <v>1.9472361809045227E-2</v>
       </c>
       <c r="P74">
-        <f t="shared" si="8"/>
+        <f>J74/D74</f>
         <v>0</v>
       </c>
     </row>
@@ -4381,15 +4380,15 @@
         <v>0</v>
       </c>
       <c r="N75">
-        <f t="shared" si="6"/>
+        <f>H75/B75</f>
         <v>1.9826517967781909E-2</v>
       </c>
       <c r="O75">
-        <f t="shared" si="7"/>
+        <f>I75/C75</f>
         <v>2.0202020202020204E-2</v>
       </c>
       <c r="P75">
-        <f t="shared" si="8"/>
+        <f>J75/D75</f>
         <v>0</v>
       </c>
     </row>
@@ -4434,15 +4433,15 @@
         <v>0</v>
       </c>
       <c r="N76">
-        <f t="shared" si="6"/>
+        <f>H76/B76</f>
         <v>1.9777503090234856E-2</v>
       </c>
       <c r="O76">
-        <f t="shared" si="7"/>
+        <f>I76/C76</f>
         <v>2.0100502512562814E-2</v>
       </c>
       <c r="P76">
-        <f t="shared" si="8"/>
+        <f>J76/D76</f>
         <v>0</v>
       </c>
     </row>
@@ -4487,15 +4486,15 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <f t="shared" si="6"/>
+        <f>H77/B77</f>
         <v>2.1406727828746176E-2</v>
       </c>
       <c r="O77">
-        <f t="shared" si="7"/>
+        <f>I77/C77</f>
         <v>2.1998742928975488E-2</v>
       </c>
       <c r="P77">
-        <f t="shared" si="8"/>
+        <f>J77/D77</f>
         <v>0</v>
       </c>
     </row>
@@ -4540,15 +4539,15 @@
         <v>0</v>
       </c>
       <c r="N78">
-        <f t="shared" si="6"/>
+        <f>H78/B78</f>
         <v>2.1329987452948559E-2</v>
       </c>
       <c r="O78">
-        <f t="shared" si="7"/>
+        <f>I78/C78</f>
         <v>2.1725239616613417E-2</v>
       </c>
       <c r="P78">
-        <f t="shared" si="8"/>
+        <f>J78/D78</f>
         <v>0</v>
       </c>
     </row>
@@ -4593,15 +4592,15 @@
         <v>0</v>
       </c>
       <c r="N79">
-        <f t="shared" si="6"/>
+        <f>H79/B79</f>
         <v>1.8668326073428748E-2</v>
       </c>
       <c r="O79">
-        <f t="shared" si="7"/>
+        <f>I79/C79</f>
         <v>1.8975332068311195E-2</v>
       </c>
       <c r="P79">
-        <f t="shared" si="8"/>
+        <f>J79/D79</f>
         <v>0</v>
       </c>
     </row>
@@ -4646,15 +4645,15 @@
         <v>1</v>
       </c>
       <c r="N80">
-        <f t="shared" si="6"/>
+        <f>H80/B80</f>
         <v>1.9387116948092559E-2</v>
       </c>
       <c r="O80">
-        <f t="shared" si="7"/>
+        <f>I80/C80</f>
         <v>1.9023462270133164E-2</v>
       </c>
       <c r="P80">
-        <f t="shared" si="8"/>
+        <f>J80/D80</f>
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
@@ -4699,15 +4698,15 @@
         <v>0</v>
       </c>
       <c r="N81">
-        <f t="shared" si="6"/>
+        <f>H81/B81</f>
         <v>1.8450184501845018E-2</v>
       </c>
       <c r="O81">
-        <f t="shared" si="7"/>
+        <f>I81/C81</f>
         <v>1.8761726078799251E-2</v>
       </c>
       <c r="P81">
-        <f t="shared" si="8"/>
+        <f>J81/D81</f>
         <v>0</v>
       </c>
     </row>
@@ -4752,15 +4751,15 @@
         <v>0</v>
       </c>
       <c r="N82">
-        <f t="shared" si="6"/>
+        <f>H82/B82</f>
         <v>1.5479876160990712E-2</v>
       </c>
       <c r="O82">
-        <f t="shared" si="7"/>
+        <f>I82/C82</f>
         <v>1.5743073047858942E-2</v>
       </c>
       <c r="P82">
-        <f t="shared" si="8"/>
+        <f>J82/D82</f>
         <v>0</v>
       </c>
     </row>
@@ -4805,15 +4804,15 @@
         <v>1</v>
       </c>
       <c r="N83">
-        <f t="shared" si="6"/>
+        <f>H83/B83</f>
         <v>1.8091079226450407E-2</v>
       </c>
       <c r="O83">
-        <f t="shared" si="7"/>
+        <f>I83/C83</f>
         <v>1.7743979721166033E-2</v>
       </c>
       <c r="P83">
-        <f t="shared" si="8"/>
+        <f>J83/D83</f>
         <v>0.04</v>
       </c>
     </row>
@@ -4858,15 +4857,15 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <f t="shared" si="6"/>
+        <f>H84/B84</f>
         <v>1.7846153846153845E-2</v>
       </c>
       <c r="O84">
-        <f t="shared" si="7"/>
+        <f>I84/C84</f>
         <v>1.8124999999999999E-2</v>
       </c>
       <c r="P84">
-        <f t="shared" si="8"/>
+        <f>J84/D84</f>
         <v>0</v>
       </c>
     </row>
@@ -4911,15 +4910,15 @@
         <v>0</v>
       </c>
       <c r="N85">
-        <f t="shared" si="6"/>
+        <f>H85/B85</f>
         <v>1.6079158936301793E-2</v>
       </c>
       <c r="O85">
-        <f t="shared" si="7"/>
+        <f>I85/C85</f>
         <v>1.6300940438871474E-2</v>
       </c>
       <c r="P85">
-        <f t="shared" si="8"/>
+        <f>J85/D85</f>
         <v>0</v>
       </c>
     </row>
@@ -4964,15 +4963,15 @@
         <v>0</v>
       </c>
       <c r="N86">
-        <f t="shared" si="6"/>
+        <f>H86/B86</f>
         <v>1.6707920792079209E-2</v>
       </c>
       <c r="O86">
-        <f t="shared" si="7"/>
+        <f>I86/C86</f>
         <v>1.7013232514177693E-2</v>
       </c>
       <c r="P86">
-        <f t="shared" si="8"/>
+        <f>J86/D86</f>
         <v>0</v>
       </c>
     </row>
@@ -5017,15 +5016,15 @@
         <v>0</v>
       </c>
       <c r="N87">
-        <f t="shared" si="6"/>
+        <f>H87/B87</f>
         <v>1.9338739862757331E-2</v>
       </c>
       <c r="O87">
-        <f t="shared" si="7"/>
+        <f>I87/C87</f>
         <v>1.9682539682539683E-2</v>
       </c>
       <c r="P87">
-        <f t="shared" si="8"/>
+        <f>J87/D87</f>
         <v>0</v>
       </c>
     </row>
@@ -5070,15 +5069,15 @@
         <v>1</v>
       </c>
       <c r="N88">
-        <f t="shared" si="6"/>
+        <f>H88/B88</f>
         <v>2.3009950248756218E-2</v>
       </c>
       <c r="O88">
-        <f t="shared" si="7"/>
+        <f>I88/C88</f>
         <v>2.2929936305732482E-2</v>
       </c>
       <c r="P88">
-        <f t="shared" si="8"/>
+        <f>J88/D88</f>
         <v>2.6315789473684209E-2</v>
       </c>
     </row>
@@ -5123,15 +5122,15 @@
         <v>0</v>
       </c>
       <c r="N89">
-        <f t="shared" si="6"/>
+        <f>H89/B89</f>
         <v>1.6605166051660517E-2</v>
       </c>
       <c r="O89">
-        <f t="shared" si="7"/>
+        <f>I89/C89</f>
         <v>1.6853932584269662E-2</v>
       </c>
       <c r="P89">
-        <f t="shared" si="8"/>
+        <f>J89/D89</f>
         <v>0</v>
       </c>
     </row>
@@ -5176,15 +5175,15 @@
         <v>0</v>
       </c>
       <c r="N90">
-        <f t="shared" si="6"/>
+        <f>H90/B90</f>
         <v>1.5365703749231715E-2</v>
       </c>
       <c r="O90">
-        <f t="shared" si="7"/>
+        <f>I90/C90</f>
         <v>1.5625E-2</v>
       </c>
       <c r="P90">
-        <f t="shared" si="8"/>
+        <f>J90/D90</f>
         <v>0</v>
       </c>
     </row>
@@ -5229,15 +5228,15 @@
         <v>0</v>
       </c>
       <c r="N91">
-        <f t="shared" si="6"/>
+        <f>H91/B91</f>
         <v>1.5337423312883436E-2</v>
       </c>
       <c r="O91">
-        <f t="shared" si="7"/>
+        <f>I91/C91</f>
         <v>1.5595757953836557E-2</v>
       </c>
       <c r="P91">
-        <f t="shared" si="8"/>
+        <f>J91/D91</f>
         <v>0</v>
       </c>
     </row>
@@ -5282,15 +5281,15 @@
         <v>0</v>
       </c>
       <c r="N92">
-        <f t="shared" si="6"/>
+        <f>H92/B92</f>
         <v>2.2657685241886098E-2</v>
       </c>
       <c r="O92">
-        <f t="shared" si="7"/>
+        <f>I92/C92</f>
         <v>2.3052959501557634E-2</v>
       </c>
       <c r="P92">
-        <f t="shared" si="8"/>
+        <f>J92/D92</f>
         <v>0</v>
       </c>
     </row>
@@ -5335,15 +5334,15 @@
         <v>0</v>
       </c>
       <c r="N93">
-        <f t="shared" si="6"/>
+        <f>H93/B93</f>
         <v>1.488833746898263E-2</v>
       </c>
       <c r="O93">
-        <f t="shared" si="7"/>
+        <f>I93/C93</f>
         <v>1.5257469802924348E-2</v>
       </c>
       <c r="P93">
-        <f t="shared" si="8"/>
+        <f>J93/D93</f>
         <v>0</v>
       </c>
     </row>
@@ -5388,15 +5387,15 @@
         <v>0</v>
       </c>
       <c r="N94">
-        <f t="shared" si="6"/>
+        <f>H94/B94</f>
         <v>2.1276595744680851E-2</v>
       </c>
       <c r="O94">
-        <f t="shared" si="7"/>
+        <f>I94/C94</f>
         <v>2.1573604060913704E-2</v>
       </c>
       <c r="P94">
-        <f t="shared" si="8"/>
+        <f>J94/D94</f>
         <v>0</v>
       </c>
     </row>
@@ -5441,15 +5440,15 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <f t="shared" si="6"/>
+        <f>H95/B95</f>
         <v>1.7890191239975324E-2</v>
       </c>
       <c r="O95">
-        <f t="shared" si="7"/>
+        <f>I95/C95</f>
         <v>1.7621145374449341E-2</v>
       </c>
       <c r="P95">
-        <f t="shared" si="8"/>
+        <f>J95/D95</f>
         <v>3.125E-2</v>
       </c>
     </row>
@@ -5494,19 +5493,19 @@
         <v>0</v>
       </c>
       <c r="N96">
-        <f t="shared" si="6"/>
+        <f>H96/B96</f>
         <v>1.4814814814814815E-2</v>
       </c>
       <c r="O96">
-        <f t="shared" si="7"/>
+        <f>I96/C96</f>
         <v>1.5103838892385148E-2</v>
       </c>
       <c r="P96">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J96/D96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1913</v>
       </c>
@@ -5547,19 +5546,19 @@
         <v>0</v>
       </c>
       <c r="N97">
-        <f t="shared" si="6"/>
+        <f>H97/B97</f>
         <v>2.1144278606965175E-2</v>
       </c>
       <c r="O97">
-        <f t="shared" si="7"/>
+        <f>I97/C97</f>
         <v>2.155992390615092E-2</v>
       </c>
       <c r="P97">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J97/D97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1913</v>
       </c>
@@ -5600,19 +5599,19 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <f t="shared" si="6"/>
+        <f>H98/B98</f>
         <v>1.86219739292365E-2</v>
       </c>
       <c r="O98">
-        <f t="shared" si="7"/>
+        <f>I98/C98</f>
         <v>1.9011406844106463E-2</v>
       </c>
       <c r="P98">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J98/D98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1913</v>
       </c>
@@ -5653,19 +5652,19 @@
         <v>0</v>
       </c>
       <c r="N99">
-        <f t="shared" ref="N99:N112" si="9">H99/B99</f>
+        <f>H99/B99</f>
         <v>1.7835178351783519E-2</v>
       </c>
       <c r="O99">
-        <f t="shared" ref="O99:O112" si="10">I99/C99</f>
+        <f>I99/C99</f>
         <v>1.8238993710691823E-2</v>
       </c>
       <c r="P99">
-        <f t="shared" ref="P99:P112" si="11">J99/D99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J99/D99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1913</v>
       </c>
@@ -5706,19 +5705,19 @@
         <v>0</v>
       </c>
       <c r="N100">
-        <f t="shared" si="9"/>
+        <f>H100/B100</f>
         <v>2.0171149144254278E-2</v>
       </c>
       <c r="O100">
-        <f t="shared" si="10"/>
+        <f>I100/C100</f>
         <v>2.0560747663551402E-2</v>
       </c>
       <c r="P100">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J100/D100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1913</v>
       </c>
@@ -5759,19 +5758,19 @@
         <v>0</v>
       </c>
       <c r="N101">
-        <f t="shared" si="9"/>
+        <f>H101/B101</f>
         <v>1.9619865113427344E-2</v>
       </c>
       <c r="O101">
-        <f t="shared" si="10"/>
+        <f>I101/C101</f>
         <v>2.0062695924764892E-2</v>
       </c>
       <c r="P101">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J101/D101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1913</v>
       </c>
@@ -5812,684 +5811,85 @@
         <v>0</v>
       </c>
       <c r="N102">
-        <f t="shared" si="9"/>
+        <f>H102/B102</f>
         <v>1.4814814814814815E-2</v>
       </c>
       <c r="O102">
-        <f t="shared" si="10"/>
+        <f>I102/C102</f>
         <v>1.4925373134328358E-2</v>
       </c>
       <c r="P102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>4783</v>
-      </c>
-      <c r="B103">
-        <v>4048</v>
-      </c>
-      <c r="C103">
-        <v>3997</v>
-      </c>
-      <c r="D103">
-        <v>51</v>
-      </c>
-      <c r="E103">
-        <v>51</v>
-      </c>
-      <c r="F103">
-        <v>50</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>46</v>
-      </c>
-      <c r="I103">
-        <v>46</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L103">
-        <v>0.92</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O103">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P103">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>4783</v>
-      </c>
-      <c r="B104">
-        <v>4048</v>
-      </c>
-      <c r="C104">
-        <v>3997</v>
-      </c>
-      <c r="D104">
-        <v>51</v>
-      </c>
-      <c r="E104">
-        <v>51</v>
-      </c>
-      <c r="F104">
-        <v>50</v>
-      </c>
-      <c r="G104">
-        <v>1</v>
-      </c>
-      <c r="H104">
-        <v>46</v>
-      </c>
-      <c r="I104">
-        <v>46</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L104">
-        <v>0.92</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O104">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P104">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+        <f>J102/D102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>4783</v>
-      </c>
-      <c r="B105">
-        <v>4048</v>
-      </c>
-      <c r="C105">
-        <v>3997</v>
-      </c>
-      <c r="D105">
-        <v>51</v>
-      </c>
-      <c r="E105">
-        <v>51</v>
-      </c>
-      <c r="F105">
-        <v>50</v>
-      </c>
-      <c r="G105">
-        <v>1</v>
-      </c>
-      <c r="H105">
-        <v>46</v>
-      </c>
-      <c r="I105">
-        <v>46</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L105">
-        <v>0.92</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O105">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P105">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>4783</v>
-      </c>
-      <c r="B106">
-        <v>4048</v>
-      </c>
-      <c r="C106">
-        <v>3997</v>
-      </c>
-      <c r="D106">
-        <v>51</v>
-      </c>
-      <c r="E106">
-        <v>51</v>
-      </c>
-      <c r="F106">
-        <v>50</v>
-      </c>
-      <c r="G106">
-        <v>1</v>
-      </c>
-      <c r="H106">
-        <v>46</v>
-      </c>
-      <c r="I106">
-        <v>46</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L106">
-        <v>0.92</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O106">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P106">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>4783</v>
-      </c>
-      <c r="B107">
-        <v>4048</v>
-      </c>
-      <c r="C107">
-        <v>3997</v>
-      </c>
-      <c r="D107">
-        <v>51</v>
-      </c>
-      <c r="E107">
-        <v>51</v>
-      </c>
-      <c r="F107">
-        <v>50</v>
-      </c>
-      <c r="G107">
-        <v>1</v>
-      </c>
-      <c r="H107">
-        <v>46</v>
-      </c>
-      <c r="I107">
-        <v>46</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L107">
-        <v>0.92</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O107">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P107">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>4783</v>
-      </c>
-      <c r="B108">
-        <v>4048</v>
-      </c>
-      <c r="C108">
-        <v>3997</v>
-      </c>
-      <c r="D108">
-        <v>51</v>
-      </c>
-      <c r="E108">
-        <v>51</v>
-      </c>
-      <c r="F108">
-        <v>50</v>
-      </c>
-      <c r="G108">
-        <v>1</v>
-      </c>
-      <c r="H108">
-        <v>46</v>
-      </c>
-      <c r="I108">
-        <v>46</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L108">
-        <v>0.92</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O108">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P108">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>4783</v>
-      </c>
-      <c r="B109">
-        <v>4088</v>
-      </c>
-      <c r="C109">
-        <v>4063</v>
-      </c>
-      <c r="D109">
-        <v>25</v>
-      </c>
-      <c r="E109">
-        <v>51</v>
-      </c>
-      <c r="F109">
-        <v>50</v>
-      </c>
-      <c r="G109">
-        <v>1</v>
-      </c>
-      <c r="H109">
-        <v>46</v>
-      </c>
-      <c r="I109">
-        <v>46</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L109">
-        <v>0.92</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <f t="shared" si="9"/>
-        <v>1.1252446183953033E-2</v>
-      </c>
-      <c r="O109">
-        <f t="shared" si="10"/>
-        <v>1.1321683485109525E-2</v>
-      </c>
-      <c r="P109">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>4783</v>
-      </c>
-      <c r="B110">
-        <v>4048</v>
-      </c>
-      <c r="C110">
-        <v>3997</v>
-      </c>
-      <c r="D110">
-        <v>51</v>
-      </c>
-      <c r="E110">
-        <v>51</v>
-      </c>
-      <c r="F110">
-        <v>50</v>
-      </c>
-      <c r="G110">
-        <v>1</v>
-      </c>
-      <c r="H110">
-        <v>46</v>
-      </c>
-      <c r="I110">
-        <v>46</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L110">
-        <v>0.92</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O110">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P110">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>4783</v>
-      </c>
-      <c r="B111">
-        <v>4048</v>
-      </c>
-      <c r="C111">
-        <v>3997</v>
-      </c>
-      <c r="D111">
-        <v>51</v>
-      </c>
-      <c r="E111">
-        <v>51</v>
-      </c>
-      <c r="F111">
-        <v>50</v>
-      </c>
-      <c r="G111">
-        <v>1</v>
-      </c>
-      <c r="H111">
-        <v>46</v>
-      </c>
-      <c r="I111">
-        <v>46</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L111">
-        <v>0.92</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O111">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P111">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>4783</v>
-      </c>
-      <c r="B112">
-        <v>4048</v>
-      </c>
-      <c r="C112">
-        <v>3997</v>
-      </c>
-      <c r="D112">
-        <v>51</v>
-      </c>
-      <c r="E112">
-        <v>51</v>
-      </c>
-      <c r="F112">
-        <v>50</v>
-      </c>
-      <c r="G112">
-        <v>1</v>
-      </c>
-      <c r="H112">
-        <v>46</v>
-      </c>
-      <c r="I112">
-        <v>46</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0.90196078431372551</v>
-      </c>
-      <c r="L112">
-        <v>0.92</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <f t="shared" si="9"/>
-        <v>1.1363636363636364E-2</v>
-      </c>
-      <c r="O112">
-        <f t="shared" si="10"/>
-        <v>1.1508631473605204E-2</v>
-      </c>
-      <c r="P112">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <f>AVERAGE(A103:A112)</f>
-        <v>4783</v>
-      </c>
-      <c r="B115">
-        <f t="shared" ref="B115:P115" si="12">AVERAGE(B103:B112)</f>
-        <v>4052</v>
-      </c>
-      <c r="C115">
-        <f t="shared" si="12"/>
-        <v>4003.6</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="12"/>
-        <v>48.4</v>
-      </c>
-      <c r="E115">
-        <f t="shared" si="12"/>
-        <v>51</v>
-      </c>
-      <c r="F115">
-        <f t="shared" si="12"/>
-        <v>50</v>
-      </c>
-      <c r="G115">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="H115">
-        <f t="shared" si="12"/>
-        <v>46</v>
-      </c>
-      <c r="I115">
-        <f t="shared" si="12"/>
-        <v>46</v>
-      </c>
-      <c r="J115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <f t="shared" si="12"/>
-        <v>0.90196078431372562</v>
-      </c>
-      <c r="L115">
-        <f t="shared" si="12"/>
-        <v>0.92000000000000015</v>
-      </c>
-      <c r="M115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <f t="shared" si="12"/>
-        <v>1.1352517345668032E-2</v>
-      </c>
-      <c r="O115">
-        <f t="shared" si="12"/>
-        <v>1.1489936674755636E-2</v>
-      </c>
-      <c r="P115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A116">
         <f>AVERAGE(A3:A102)</f>
         <v>1912.9</v>
       </c>
-      <c r="B116">
-        <f t="shared" ref="B116:P116" si="13">AVERAGE(B3:B102)</f>
+      <c r="B105">
+        <f>AVERAGE(B3:B102)</f>
         <v>1616.5</v>
       </c>
-      <c r="C116">
-        <f t="shared" si="13"/>
+      <c r="C105">
+        <f>AVERAGE(C3:C102)</f>
         <v>1589.34</v>
       </c>
-      <c r="D116">
-        <f t="shared" si="13"/>
+      <c r="D105">
+        <f>AVERAGE(D3:D102)</f>
         <v>27.16</v>
       </c>
-      <c r="E116">
-        <f t="shared" si="13"/>
+      <c r="E105">
+        <f>AVERAGE(E3:E102)</f>
         <v>31.04</v>
       </c>
-      <c r="F116">
-        <f t="shared" si="13"/>
+      <c r="F105">
+        <f>AVERAGE(F3:F102)</f>
         <v>30.55</v>
       </c>
-      <c r="G116">
-        <f t="shared" si="13"/>
+      <c r="G105">
+        <f>AVERAGE(G3:G102)</f>
         <v>0.49</v>
       </c>
-      <c r="H116">
-        <f t="shared" si="13"/>
+      <c r="H105">
+        <f>AVERAGE(H3:H102)</f>
         <v>28.89</v>
       </c>
-      <c r="I116">
-        <f t="shared" si="13"/>
+      <c r="I105">
+        <f>AVERAGE(I3:I102)</f>
         <v>28.63</v>
       </c>
-      <c r="J116">
-        <f t="shared" si="13"/>
+      <c r="J105">
+        <f>AVERAGE(J3:J102)</f>
         <v>0.26</v>
       </c>
-      <c r="K116">
-        <f t="shared" si="13"/>
+      <c r="K105" s="3">
+        <f>AVERAGE(K3:K102)</f>
         <v>0.93201322179392621</v>
       </c>
-      <c r="L116">
-        <f t="shared" si="13"/>
+      <c r="L105" s="3">
+        <f>AVERAGE(L3:L102)</f>
         <v>0.93833192745302185</v>
       </c>
-      <c r="M116">
-        <f t="shared" si="13"/>
+      <c r="M105" s="3">
+        <f>AVERAGE(M3:M102)</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="N116">
-        <f t="shared" si="13"/>
+      <c r="N105" s="3">
+        <f>AVERAGE(N3:N102)</f>
         <v>1.7874938991986077E-2</v>
       </c>
-      <c r="O116">
-        <f t="shared" si="13"/>
+      <c r="O105" s="3">
+        <f>AVERAGE(O3:O102)</f>
         <v>1.8017936690040214E-2</v>
       </c>
-      <c r="P116">
-        <f t="shared" si="13"/>
+      <c r="P105" s="3">
+        <f>AVERAGE(P3:P102)</f>
         <v>1.0587552771074794E-2</v>
       </c>
-      <c r="Q116" t="s">
-        <v>17</v>
+      <c r="Q105" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6500,4 +5900,660 @@
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4728BD-F53F-4E10-A9F0-3866CE4736F2}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4783</v>
+      </c>
+      <c r="B2">
+        <v>4048</v>
+      </c>
+      <c r="C2">
+        <v>3997</v>
+      </c>
+      <c r="D2">
+        <v>51</v>
+      </c>
+      <c r="E2">
+        <v>51</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
+        <v>46</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L2">
+        <v>0.92</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>H2/B2</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O2">
+        <f>I2/C2</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P2">
+        <f>J2/D2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4783</v>
+      </c>
+      <c r="B3">
+        <v>4048</v>
+      </c>
+      <c r="C3">
+        <v>3997</v>
+      </c>
+      <c r="D3">
+        <v>51</v>
+      </c>
+      <c r="E3">
+        <v>51</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <v>46</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L3">
+        <v>0.92</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>H3/B3</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O3">
+        <f>I3/C3</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P3">
+        <f>J3/D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4783</v>
+      </c>
+      <c r="B4">
+        <v>4048</v>
+      </c>
+      <c r="C4">
+        <v>3997</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
+      </c>
+      <c r="E4">
+        <v>51</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>46</v>
+      </c>
+      <c r="I4">
+        <v>46</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L4">
+        <v>0.92</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>H4/B4</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O4">
+        <f>I4/C4</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P4">
+        <f>J4/D4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4783</v>
+      </c>
+      <c r="B5">
+        <v>4048</v>
+      </c>
+      <c r="C5">
+        <v>3997</v>
+      </c>
+      <c r="D5">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>46</v>
+      </c>
+      <c r="I5">
+        <v>46</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L5">
+        <v>0.92</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f>H5/B5</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O5">
+        <f>I5/C5</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P5">
+        <f>J5/D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4783</v>
+      </c>
+      <c r="B6">
+        <v>4048</v>
+      </c>
+      <c r="C6">
+        <v>3997</v>
+      </c>
+      <c r="D6">
+        <v>51</v>
+      </c>
+      <c r="E6">
+        <v>51</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>46</v>
+      </c>
+      <c r="I6">
+        <v>46</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L6">
+        <v>0.92</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>H6/B6</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O6">
+        <f>I6/C6</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P6">
+        <f>J6/D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4783</v>
+      </c>
+      <c r="B7">
+        <v>4048</v>
+      </c>
+      <c r="C7">
+        <v>3997</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>46</v>
+      </c>
+      <c r="I7">
+        <v>46</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L7">
+        <v>0.92</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f>H7/B7</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O7">
+        <f>I7/C7</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P7">
+        <f>J7/D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4783</v>
+      </c>
+      <c r="B8">
+        <v>4088</v>
+      </c>
+      <c r="C8">
+        <v>4063</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>46</v>
+      </c>
+      <c r="I8">
+        <v>46</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L8">
+        <v>0.92</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f>H8/B8</f>
+        <v>1.1252446183953033E-2</v>
+      </c>
+      <c r="O8">
+        <f>I8/C8</f>
+        <v>1.1321683485109525E-2</v>
+      </c>
+      <c r="P8">
+        <f>J8/D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4783</v>
+      </c>
+      <c r="B9">
+        <v>4048</v>
+      </c>
+      <c r="C9">
+        <v>3997</v>
+      </c>
+      <c r="D9">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>46</v>
+      </c>
+      <c r="I9">
+        <v>46</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L9">
+        <v>0.92</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f>H9/B9</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O9">
+        <f>I9/C9</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P9">
+        <f>J9/D9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4783</v>
+      </c>
+      <c r="B10">
+        <v>4048</v>
+      </c>
+      <c r="C10">
+        <v>3997</v>
+      </c>
+      <c r="D10">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>51</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>46</v>
+      </c>
+      <c r="I10">
+        <v>46</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L10">
+        <v>0.92</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <f>H10/B10</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O10">
+        <f>I10/C10</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P10">
+        <f>J10/D10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>4783</v>
+      </c>
+      <c r="B11">
+        <v>4048</v>
+      </c>
+      <c r="C11">
+        <v>3997</v>
+      </c>
+      <c r="D11">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>51</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>46</v>
+      </c>
+      <c r="I11">
+        <v>46</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.90196078431372551</v>
+      </c>
+      <c r="L11">
+        <v>0.92</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <f>H11/B11</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="O11">
+        <f>I11/C11</f>
+        <v>1.1508631473605204E-2</v>
+      </c>
+      <c r="P11">
+        <f>J11/D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f>AVERAGE(A2:A11)</f>
+        <v>4783</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13:P13" si="0">AVERAGE(B2:B11)</f>
+        <v>4052</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>4003.6</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>48.4</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.90196078431372562</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1352517345668032E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1489936674755636E-2</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>